--- a/отчеты для СН/ПОКОМ КИ/Мелитополь ПОКОМ КИ.xlsx
+++ b/отчеты для СН/ПОКОМ КИ/Мелитополь ПОКОМ КИ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\отчеты для СН\ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23155BC-F367-42E0-B049-E8D9E7C93C51}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB0C6E37-B32E-4F3F-AA58-F5EE9EF2E4BC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -569,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.85546875" bestFit="1" customWidth="1"/>
@@ -583,7 +583,7 @@
     <col min="9" max="9" width="2.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>14</v>
       </c>
@@ -595,7 +595,7 @@
       <c r="G1" s="11"/>
       <c r="H1" s="5"/>
     </row>
-    <row r="2" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6"/>
       <c r="B2" s="7"/>
       <c r="C2" s="8" t="s">
@@ -617,7 +617,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -631,17 +631,22 @@
         <v>11.7</v>
       </c>
       <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
+      <c r="F3" s="4">
+        <v>3.8</v>
+      </c>
       <c r="G3" s="4">
         <f t="shared" ref="G3:G14" si="0">D3+E3-F3</f>
-        <v>11.7</v>
+        <v>7.8999999999999995</v>
       </c>
       <c r="H3" s="4">
         <f>3*J3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11.399999999999999</v>
+      </c>
+      <c r="J3">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -653,20 +658,22 @@
       </c>
       <c r="D4" s="3">
         <f t="shared" ref="D4:D14" si="1">G3</f>
-        <v>11.7</v>
-      </c>
-      <c r="E4" s="4"/>
+        <v>7.8999999999999995</v>
+      </c>
+      <c r="E4" s="4">
+        <v>13</v>
+      </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>11.7</v>
+        <v>20.9</v>
       </c>
       <c r="H4" s="4">
         <f>H3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11.399999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -678,20 +685,20 @@
       </c>
       <c r="D5" s="3">
         <f t="shared" si="1"/>
-        <v>11.7</v>
+        <v>20.9</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4">
         <f t="shared" si="0"/>
-        <v>11.7</v>
+        <v>20.9</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" ref="H5:H14" si="2">H4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11.399999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -703,20 +710,22 @@
       </c>
       <c r="D6" s="3">
         <f t="shared" si="1"/>
-        <v>11.7</v>
+        <v>20.9</v>
       </c>
       <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+      <c r="F6" s="4">
+        <v>3.8</v>
+      </c>
       <c r="G6" s="4">
         <f t="shared" si="0"/>
-        <v>11.7</v>
+        <v>17.099999999999998</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11.399999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -728,20 +737,22 @@
       </c>
       <c r="D7" s="3">
         <f t="shared" si="1"/>
-        <v>11.7</v>
+        <v>17.099999999999998</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+      <c r="F7" s="4">
+        <v>3.8</v>
+      </c>
       <c r="G7" s="4">
         <f t="shared" si="0"/>
-        <v>11.7</v>
+        <v>13.299999999999997</v>
       </c>
       <c r="H7" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11.399999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -753,20 +764,24 @@
       </c>
       <c r="D8" s="3">
         <f t="shared" si="1"/>
-        <v>11.7</v>
-      </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+        <v>13.299999999999997</v>
+      </c>
+      <c r="E8" s="4">
+        <v>17.3</v>
+      </c>
+      <c r="F8" s="4">
+        <v>3.8</v>
+      </c>
       <c r="G8" s="4">
         <f t="shared" si="0"/>
-        <v>11.7</v>
+        <v>26.799999999999997</v>
       </c>
       <c r="H8" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11.399999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -778,20 +793,24 @@
       </c>
       <c r="D9" s="3">
         <f t="shared" si="1"/>
-        <v>11.7</v>
-      </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+        <v>26.799999999999997</v>
+      </c>
+      <c r="E9" s="4">
+        <v>9.9</v>
+      </c>
+      <c r="F9" s="4">
+        <v>3.8</v>
+      </c>
       <c r="G9" s="4">
         <f t="shared" si="0"/>
-        <v>11.7</v>
+        <v>32.9</v>
       </c>
       <c r="H9" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11.399999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -803,20 +822,22 @@
       </c>
       <c r="D10" s="3">
         <f t="shared" si="1"/>
-        <v>11.7</v>
+        <v>32.9</v>
       </c>
       <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+      <c r="F10" s="4">
+        <v>3.8</v>
+      </c>
       <c r="G10" s="4">
         <f t="shared" si="0"/>
-        <v>11.7</v>
+        <v>29.099999999999998</v>
       </c>
       <c r="H10" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11.399999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -828,20 +849,20 @@
       </c>
       <c r="D11" s="3">
         <f t="shared" si="1"/>
-        <v>11.7</v>
+        <v>29.099999999999998</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4">
         <f t="shared" si="0"/>
-        <v>11.7</v>
+        <v>29.099999999999998</v>
       </c>
       <c r="H11" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11.399999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -853,20 +874,20 @@
       </c>
       <c r="D12" s="3">
         <f t="shared" si="1"/>
-        <v>11.7</v>
+        <v>29.099999999999998</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4">
         <f t="shared" si="0"/>
-        <v>11.7</v>
+        <v>29.099999999999998</v>
       </c>
       <c r="H12" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11.399999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -878,20 +899,22 @@
       </c>
       <c r="D13" s="3">
         <f t="shared" si="1"/>
-        <v>11.7</v>
+        <v>29.099999999999998</v>
       </c>
       <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
+      <c r="F13" s="4">
+        <v>3.8</v>
+      </c>
       <c r="G13" s="4">
         <f t="shared" si="0"/>
-        <v>11.7</v>
+        <v>25.299999999999997</v>
       </c>
       <c r="H13" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11.399999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -903,20 +926,22 @@
       </c>
       <c r="D14" s="3">
         <f t="shared" si="1"/>
-        <v>11.7</v>
+        <v>25.299999999999997</v>
       </c>
       <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
+      <c r="F14" s="4">
+        <v>3.8</v>
+      </c>
       <c r="G14" s="4">
         <f t="shared" si="0"/>
-        <v>11.7</v>
+        <v>21.499999999999996</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+        <v>11.399999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -925,11 +950,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="4">
         <f>SUM(E3:E14)</f>
-        <v>0</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="F15" s="4">
         <f>SUM(F3:F14)</f>
-        <v>0</v>
+        <v>30.400000000000002</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>

--- a/отчеты для СН/ПОКОМ КИ/Мелитополь ПОКОМ КИ.xlsx
+++ b/отчеты для СН/ПОКОМ КИ/Мелитополь ПОКОМ КИ.xlsx
@@ -1,29 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\отчеты для СН\ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\отчеты для СН\ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB0C6E37-B32E-4F3F-AA58-F5EE9EF2E4BC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B4F201-5EDF-4365-BF47-37ED2E72E3A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="КИ" sheetId="6" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" refMode="R1C1"/>
 </workbook>
 </file>
 
@@ -182,12 +174,12 @@
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -795,15 +787,13 @@
         <f t="shared" si="1"/>
         <v>26.799999999999997</v>
       </c>
-      <c r="E9" s="4">
-        <v>9.9</v>
-      </c>
+      <c r="E9" s="4"/>
       <c r="F9" s="4">
         <v>3.8</v>
       </c>
       <c r="G9" s="4">
         <f t="shared" si="0"/>
-        <v>32.9</v>
+        <v>22.999999999999996</v>
       </c>
       <c r="H9" s="4">
         <f t="shared" si="2"/>
@@ -822,9 +812,11 @@
       </c>
       <c r="D10" s="3">
         <f t="shared" si="1"/>
-        <v>32.9</v>
-      </c>
-      <c r="E10" s="4"/>
+        <v>22.999999999999996</v>
+      </c>
+      <c r="E10" s="4">
+        <v>9.9</v>
+      </c>
       <c r="F10" s="4">
         <v>3.8</v>
       </c>
